--- a/Part Lists/Electronics.xlsx
+++ b/Part Lists/Electronics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vbp/Documents/GitHub/FP_V3/Part Lists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142448C5-4E06-D940-B2DF-7E0B4902814F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468C0725-9A4C-C04E-9323-B4D3389BDEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34220" yWindow="7040" windowWidth="26840" windowHeight="15680" xr2:uid="{21FB6E91-6764-104E-8462-25D94EB2C132}"/>
+    <workbookView xWindow="-34300" yWindow="8000" windowWidth="26840" windowHeight="15680" xr2:uid="{21FB6E91-6764-104E-8462-25D94EB2C132}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>USB 2.0 A Male to USB 2.0 Micro Cable 6'</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/qualtek/3021007-06/1531291?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=23152963569&amp;gbraid=0AAAAADrbLljtgW-U5wQnGGsjyvQ_EuEtO&amp;gclid=CjwKCAjw2aPVBhBkEiwA0Cptt6EpUDDrmpLN7JY8X76w1EzuMKHRf_jM6CvvGGjJN5x_6hjZCcWMKxoC_p8QAvD_BwE</t>
+  </si>
+  <si>
+    <t>Q364-ND</t>
+  </si>
+  <si>
+    <t>See folder</t>
   </si>
 </sst>
 </file>
@@ -809,10 +818,32 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3.46</v>
+      </c>
+      <c r="G10" s="7">
+        <f>F10*C10</f>
+        <v>3.46</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -823,6 +854,7 @@
     <hyperlink ref="B7" r:id="rId4" xr:uid="{8ADA29AE-1455-5C4C-849E-AB527E5C07ED}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{E3A32E9A-A0E5-7B4A-92D7-A5295CE9F6AF}"/>
     <hyperlink ref="B9" r:id="rId6" display="https://www.digikey.ca/en/products/detail/qualtek/3025031-06/6188813?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=23152963569&amp;gbraid=0AAAAADrbLljtgW-U5wQnGGsjyvQ_EuEtO&amp;gclid=CjwKCAjw2aPVBhBkEiwA0Cpttzu4qRS3eGd9YZGWHvP3CV8hgRH_YIuRGa3XAj0O5uJc_a37Gl5WvBoC-AcQAvD_BwE" xr:uid="{F9A0D272-B4C2-854B-A5B8-B2BB7A87CF1A}"/>
+    <hyperlink ref="B10" r:id="rId7" display="https://www.digikey.ca/en/products/detail/qualtek/3021007-06/1531291?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=23152963569&amp;gbraid=0AAAAADrbLljtgW-U5wQnGGsjyvQ_EuEtO&amp;gclid=CjwKCAjw2aPVBhBkEiwA0Cptt6EpUDDrmpLN7JY8X76w1EzuMKHRf_jM6CvvGGjJN5x_6hjZCcWMKxoC_p8QAvD_BwE" xr:uid="{AD4F1F11-7616-944A-8D80-2D2158866412}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
